--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260622.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260622.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,56 +611,56 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>160,975</t>
+          <t>159,675</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.60%</t>
+          <t>26.62%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>116,810</t>
+          <t>18,275</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.96%</t>
+          <t>8.77%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>18,395</t>
+          <t>115,830</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8.63%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>59,485</t>
+          <t>59,085</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.69%</t>
+          <t>7.74%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>141,845</t>
+          <t>140,655</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.12%</t>
+          <t>5.15%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>6,665</t>
+          <t>6,565</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -743,29 +743,29 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>76,525</t>
+          <t>75,875</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>69,480</t>
+          <t>52,335</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,22 +777,22 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>52,775</t>
+          <t>68,880</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.73%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>23,085</t>
+          <t>22,895</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.63%</t>
+          <t>2.68%</t>
         </is>
       </c>
     </row>
@@ -831,56 +831,56 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>170,275,514</t>
+          <t>171,234,091</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>21,363</t>
+          <t>36,530</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>36,840</t>
+          <t>21,183</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>23,695</t>
+          <t>23,545</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -919,78 +919,78 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>89,935</t>
+          <t>89,195</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>59,655</t>
+          <t>9,300</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>13,731</t>
+          <t>59,155</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,410</t>
+          <t>13,611</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>22,790</t>
+          <t>22,600</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
@@ -1029,95 +1029,95 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>31,058</t>
+          <t>30,798</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>42,340</t>
+          <t>11,196</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>69,448</t>
+          <t>41,980</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>11,306</t>
+          <t>68,868</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>23,057</t>
+          <t>24,738</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,22 +1129,22 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>24,948</t>
+          <t>22,867</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>148,265</t>
+          <t>147,015</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>21,635</t>
+          <t>21,455</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
@@ -1205,56 +1205,56 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>18,691</t>
+          <t>18,521</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>43,850</t>
+          <t>13,665</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>13,865</t>
+          <t>43,480</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>50,510</t>
+          <t>50,090</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,51 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.41%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_NTD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>31,605,000</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>1,949,102</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
